--- a/output/graficos_regionales/plot_regional_serie_i_ingr_s_2024_valparaiso.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_s_2024_valparaiso.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:36</t>
+    <t xml:space="preserve">2026-10-05 01:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -535,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>810111.12</v>
+        <v>810111.13</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>878312.06</v>
@@ -557,7 +557,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>850768.12</v>
+        <v>850768.13</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>926506.25</v>
@@ -601,10 +601,10 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>1083458.12</v>
+        <v>1083458.13</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1163774.62</v>
+        <v>1163774.63</v>
       </c>
     </row>
     <row r="13">
